--- a/sheets/S08A22P169.xlsx
+++ b/sheets/S08A22P169.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8808" uniqueCount="2289">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8800" uniqueCount="2288">
   <si>
     <t>Voter ID</t>
   </si>
@@ -6875,9 +6875,6 @@
   </si>
   <si>
     <t>Gagan Jha</t>
-  </si>
-  <si>
-    <t>Khushi Ram Dhiman</t>
   </si>
 </sst>
 </file>
@@ -7258,7 +7255,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H1101"/>
+  <dimension ref="A1:H1100"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -35868,32 +35865,6 @@
         <v>14</v>
       </c>
     </row>
-    <row r="1101" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1101" t="s">
-        <v>11</v>
-      </c>
-      <c r="B1101" t="s">
-        <v>1836</v>
-      </c>
-      <c r="C1101" t="s">
-        <v>2288</v>
-      </c>
-      <c r="D1101" t="s">
-        <v>11</v>
-      </c>
-      <c r="E1101" t="s">
-        <v>12</v>
-      </c>
-      <c r="F1101" t="s">
-        <v>13</v>
-      </c>
-      <c r="G1101" t="s">
-        <v>13</v>
-      </c>
-      <c r="H1101" t="s">
-        <v>14</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
